--- a/data/trans_orig/P5704-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P5704-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de contar con personas que se preocupan de lo que me sucede en 2007</t>
+          <t>Población según la frecuencia de contar con personas que se preocupan de lo que me sucede en 2007 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>498588</t>
+          <t>491284</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>560277</t>
+          <t>556639</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>603242</t>
+          <t>604652</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>676769</t>
+          <t>672153</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1119703</t>
+          <t>1122469</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1212768</t>
+          <t>1213753</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>51,72%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>250677</t>
+          <t>249466</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>307147</t>
+          <t>306920</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>333562</t>
+          <t>333998</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>397587</t>
+          <t>400778</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>598423</t>
+          <t>601071</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>687160</t>
+          <t>683149</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,11%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>146437</t>
+          <t>148925</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>195934</t>
+          <t>197635</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>188875</t>
+          <t>187125</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>240761</t>
+          <t>238602</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>348580</t>
+          <t>349368</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>419134</t>
+          <t>418598</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34354</t>
+          <t>35614</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61342</t>
+          <t>61931</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>68326</t>
+          <t>69617</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>104879</t>
+          <t>104536</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>111504</t>
+          <t>110061</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>156268</t>
+          <t>155668</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>3734</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17830</t>
+          <t>17176</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6306</t>
+          <t>6137</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>20636</t>
+          <t>20879</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12475</t>
+          <t>12455</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31556</t>
+          <t>31414</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>987761</t>
+          <t>992195</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1067213</t>
+          <t>1076079</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>922134</t>
+          <t>925278</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1002402</t>
+          <t>1006693</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1934592</t>
+          <t>1937360</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2045741</t>
+          <t>2052361</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,6%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>430589</t>
+          <t>423932</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>504191</t>
+          <t>498176</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>382901</t>
+          <t>379518</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>452083</t>
+          <t>447865</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>827783</t>
+          <t>822946</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>930502</t>
+          <t>932358</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,44%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>146750</t>
+          <t>146863</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>196104</t>
+          <t>196493</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>138343</t>
+          <t>135796</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185803</t>
+          <t>187377</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>296352</t>
+          <t>297159</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>364040</t>
+          <t>364705</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20087</t>
+          <t>19986</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43681</t>
+          <t>41245</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29927</t>
+          <t>29574</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56769</t>
+          <t>55971</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55061</t>
+          <t>55574</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>91827</t>
+          <t>91210</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4931</t>
+          <t>5325</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11627</t>
+          <t>11912</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13449</t>
+          <t>14150</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>315304</t>
+          <t>312377</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>361476</t>
+          <t>359069</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>288541</t>
+          <t>290510</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>331448</t>
+          <t>332946</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>615577</t>
+          <t>615926</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>679816</t>
+          <t>677966</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>59,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>65,96%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>140662</t>
+          <t>142874</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>183223</t>
+          <t>186532</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>97267</t>
+          <t>98309</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>135630</t>
+          <t>137011</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>249187</t>
+          <t>250508</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>307816</t>
+          <t>310777</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,24%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32466</t>
+          <t>31481</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>59456</t>
+          <t>60330</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25220</t>
+          <t>25803</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>50036</t>
+          <t>47683</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>62887</t>
+          <t>62097</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>97095</t>
+          <t>98233</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,56%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16344</t>
+          <t>15998</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5654</t>
+          <t>5933</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20544</t>
+          <t>21205</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11435</t>
+          <t>10960</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29784</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -2549,97 +2549,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1178</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>7088</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>1178</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>6851</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>5901</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1178</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>8076</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1833000</t>
+          <t>1834644</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1950440</t>
+          <t>1948459</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1857345</t>
+          <t>1853243</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1973598</t>
+          <t>1969929</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3725020</t>
+          <t>3733187</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3890843</t>
+          <t>3894128</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>58,53%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>853778</t>
+          <t>855007</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>958173</t>
+          <t>958067</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,82 +2907,82 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>26,11%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>29,26%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>876</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>897641</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>850811</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>952998</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>26,57%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>25,19%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>28,21%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1770</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>1802328</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>1734535</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>1870622</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>27,09%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>26,07%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>29,26%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>876</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>897641</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>841274</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>945222</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>26,57%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>24,9%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>27,98%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1770</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1802328</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1728382</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1870158</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>27,09%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>25,98%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,12%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>344181</t>
+          <t>348583</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>425374</t>
+          <t>422460</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>372776</t>
+          <t>369511</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>446818</t>
+          <t>444594</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>742163</t>
+          <t>736502</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>845893</t>
+          <t>843129</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>68818</t>
+          <t>67226</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>104964</t>
+          <t>104532</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>116142</t>
+          <t>115279</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>164159</t>
+          <t>165480</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>193288</t>
+          <t>193783</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>252995</t>
+          <t>251358</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>4433</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19867</t>
+          <t>18691</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10370</t>
+          <t>10799</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>29080</t>
+          <t>28798</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>17455</t>
+          <t>17476</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>40192</t>
+          <t>40974</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de contar con personas que se preocupan de lo que me sucede en 2012</t>
+          <t>Población según la frecuencia de contar con personas que se preocupan de lo que me sucede en 2012 (tasa de respuesta: 99,63%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>506093</t>
+          <t>504093</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>569898</t>
+          <t>568286</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>673735</t>
+          <t>674232</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>748038</t>
+          <t>750078</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1197819</t>
+          <t>1200022</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1296696</t>
+          <t>1299566</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,49%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>257135</t>
+          <t>256587</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>315241</t>
+          <t>315619</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>398290</t>
+          <t>399458</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>469600</t>
+          <t>470191</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>671392</t>
+          <t>667044</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>760574</t>
+          <t>759857</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,03%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>96011</t>
+          <t>94191</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>137613</t>
+          <t>136049</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>124053</t>
+          <t>123416</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>171568</t>
+          <t>170500</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>229303</t>
+          <t>232111</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>293944</t>
+          <t>293748</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,77%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15277</t>
+          <t>14595</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36944</t>
+          <t>33853</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>22892</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45412</t>
+          <t>44580</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42122</t>
+          <t>41519</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71677</t>
+          <t>72585</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3295</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17051</t>
+          <t>17287</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5155</t>
+          <t>5092</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17739</t>
+          <t>18373</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11720</t>
+          <t>10385</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29085</t>
+          <t>29432</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1202384</t>
+          <t>1202753</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1291666</t>
+          <t>1293668</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>974080</t>
+          <t>967362</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1058727</t>
+          <t>1052286</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2208079</t>
+          <t>2205103</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2321990</t>
+          <t>2327491</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>62,71%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>474580</t>
+          <t>477007</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>557828</t>
+          <t>560702</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>496659</t>
+          <t>499532</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>576575</t>
+          <t>581231</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1004022</t>
+          <t>995692</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1109582</t>
+          <t>1112576</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,98%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>144166</t>
+          <t>141703</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>195914</t>
+          <t>194418</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>126232</t>
+          <t>127535</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>176431</t>
+          <t>177685</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>286691</t>
+          <t>285507</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>354284</t>
+          <t>355896</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,59%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13999</t>
+          <t>13103</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32760</t>
+          <t>32149</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26215</t>
+          <t>26743</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54085</t>
+          <t>53693</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44335</t>
+          <t>46123</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>77210</t>
+          <t>79528</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11804</t>
+          <t>12904</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>6080</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21886</t>
+          <t>21687</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10033</t>
+          <t>10851</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>27404</t>
+          <t>28993</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>283265</t>
+          <t>282112</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>328089</t>
+          <t>328396</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>297812</t>
+          <t>296362</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>340847</t>
+          <t>338917</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>594946</t>
+          <t>594710</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>654707</t>
+          <t>656987</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>70,15%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>117710</t>
+          <t>115596</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>159450</t>
+          <t>159831</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>88002</t>
+          <t>89521</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>128393</t>
+          <t>126651</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>216814</t>
+          <t>215034</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>273600</t>
+          <t>272822</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,13%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20768</t>
+          <t>20955</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>45613</t>
+          <t>45538</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>18925</t>
+          <t>20281</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>41535</t>
+          <t>45069</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>44293</t>
+          <t>44546</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>79731</t>
+          <t>78950</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1199</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11623</t>
+          <t>10619</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5759</t>
+          <t>7093</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>2246</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13977</t>
+          <t>13261</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -5508,97 +5508,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2105</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2132</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>2121</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2031190</t>
+          <t>2028286</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2150729</t>
+          <t>2146248</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1989212</t>
+          <t>1984707</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2107654</t>
+          <t>2107428</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4056622</t>
+          <t>4053792</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4219152</t>
+          <t>4219860</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>60,73%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>884098</t>
+          <t>883944</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>993326</t>
+          <t>993655</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1019354</t>
+          <t>1021258</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1131231</t>
+          <t>1135374</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1935919</t>
+          <t>1932417</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2089351</t>
+          <t>2095363</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,15%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>277390</t>
+          <t>280623</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>351511</t>
+          <t>352999</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>289702</t>
+          <t>289982</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>362196</t>
+          <t>363475</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>594438</t>
+          <t>589904</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>695781</t>
+          <t>690214</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>36226</t>
+          <t>37664</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>65491</t>
+          <t>65504</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>56033</t>
+          <t>54672</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>91076</t>
+          <t>91653</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>100723</t>
+          <t>100364</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>146836</t>
+          <t>144167</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7490</t>
+          <t>7878</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23516</t>
+          <t>25057</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14472</t>
+          <t>13467</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>33567</t>
+          <t>35594</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>25057</t>
+          <t>26567</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>50290</t>
+          <t>52393</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de contar con personas que se preocupan de lo que me sucede en 2016</t>
+          <t>Población según la frecuencia de contar con personas que se preocupan de lo que me sucede en 2016 (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>352704</t>
+          <t>349597</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>406866</t>
+          <t>406128</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>438098</t>
+          <t>440026</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>505899</t>
+          <t>505505</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>806808</t>
+          <t>807784</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>890251</t>
+          <t>895609</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>51,32%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>204551</t>
+          <t>203839</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>255497</t>
+          <t>254143</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>262981</t>
+          <t>264870</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>321704</t>
+          <t>323774</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>482104</t>
+          <t>484474</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>561501</t>
+          <t>562107</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,21%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>94002</t>
+          <t>95590</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>132921</t>
+          <t>134868</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>154833</t>
+          <t>157840</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>207183</t>
+          <t>206883</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>264412</t>
+          <t>261899</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>327760</t>
+          <t>324432</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,59%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19416</t>
+          <t>18767</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40904</t>
+          <t>38300</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25450</t>
+          <t>26492</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52907</t>
+          <t>52562</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50759</t>
+          <t>50850</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83026</t>
+          <t>83387</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>867</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10527</t>
+          <t>10584</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4790</t>
+          <t>4402</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19547</t>
+          <t>18733</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>6219</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24312</t>
+          <t>23654</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1056771</t>
+          <t>1054261</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1145362</t>
+          <t>1146118</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>997115</t>
+          <t>1002703</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1091297</t>
+          <t>1093864</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2083492</t>
+          <t>2092981</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2213620</t>
+          <t>2213335</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,62%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>607457</t>
+          <t>606842</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>691469</t>
+          <t>690094</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>594255</t>
+          <t>593934</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>682390</t>
+          <t>681927</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1230827</t>
+          <t>1214813</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1348896</t>
+          <t>1336698</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>32,99%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>253017</t>
+          <t>254265</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>315930</t>
+          <t>318552</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>225177</t>
+          <t>223257</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>287718</t>
+          <t>284901</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>492416</t>
+          <t>496692</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>582012</t>
+          <t>580084</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22409</t>
+          <t>22076</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46018</t>
+          <t>43541</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21504</t>
+          <t>21771</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44374</t>
+          <t>44071</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49174</t>
+          <t>49824</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>80392</t>
+          <t>78962</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2935</t>
+          <t>2285</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14373</t>
+          <t>13911</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3347</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16529</t>
+          <t>16309</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8190</t>
+          <t>8606</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23261</t>
+          <t>25229</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>313355</t>
+          <t>312756</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>360290</t>
+          <t>361260</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>316715</t>
+          <t>315215</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>362448</t>
+          <t>363499</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>640846</t>
+          <t>641495</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>706363</t>
+          <t>711907</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>65,12%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>145297</t>
+          <t>144367</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>190224</t>
+          <t>190383</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>142569</t>
+          <t>143701</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>187880</t>
+          <t>187605</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>302586</t>
+          <t>301672</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>367198</t>
+          <t>365857</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,46%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26258</t>
+          <t>26421</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50785</t>
+          <t>53144</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>26090</t>
+          <t>26833</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>51452</t>
+          <t>52034</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>59331</t>
+          <t>58007</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>94878</t>
+          <t>93133</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9232</t>
+          <t>9843</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>925</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11122</t>
+          <t>10390</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2977</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15501</t>
+          <t>15848</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -8467,97 +8467,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2093</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5092</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>1006</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>5033</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>5449</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1006</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>4569</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1764667</t>
+          <t>1762878</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1881372</t>
+          <t>1876225</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1789786</t>
+          <t>1796748</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1918611</t>
+          <t>1919166</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3584262</t>
+          <t>3584300</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3756676</t>
+          <t>3748685</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,4%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>988852</t>
+          <t>985811</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1098367</t>
+          <t>1097673</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1047784</t>
+          <t>1039932</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1157402</t>
+          <t>1152250</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2064574</t>
+          <t>2076192</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2216893</t>
+          <t>2224987</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,29%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>395993</t>
+          <t>397635</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>474163</t>
+          <t>475527</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>430431</t>
+          <t>435511</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>513720</t>
+          <t>515744</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>851207</t>
+          <t>846139</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>968454</t>
+          <t>958785</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,91%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>50470</t>
+          <t>48829</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>82450</t>
+          <t>80542</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>56608</t>
+          <t>56427</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>93659</t>
+          <t>92177</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>115090</t>
+          <t>112651</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>159994</t>
+          <t>162415</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5105</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20196</t>
+          <t>18457</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11752</t>
+          <t>11337</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>31233</t>
+          <t>30097</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>20219</t>
+          <t>19642</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>42016</t>
+          <t>43037</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de contar con personas que se preocupan de lo que me sucede en 2023</t>
+          <t>Población según la frecuencia de contar con personas que se preocupan de lo que me sucede en 2023 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9610,12 +9610,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>243967</t>
+          <t>242513</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>286786</t>
+          <t>285053</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9625,12 +9625,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>334109</t>
+          <t>333480</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>377263</t>
+          <t>377563</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9680,12 +9680,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>590966</t>
+          <t>592443</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>651722</t>
+          <t>649890</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9695,12 +9695,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,4%</t>
         </is>
       </c>
     </row>
@@ -9723,12 +9723,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>123775</t>
+          <t>124088</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>162784</t>
+          <t>161570</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>212975</t>
+          <t>212218</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>253498</t>
+          <t>254174</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>346156</t>
+          <t>348585</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>399673</t>
+          <t>401803</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,78%</t>
         </is>
       </c>
     </row>
@@ -9836,12 +9836,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55826</t>
+          <t>56006</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>84387</t>
+          <t>83601</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9851,12 +9851,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>86158</t>
+          <t>86524</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>113457</t>
+          <t>113085</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9886,12 +9886,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>150218</t>
+          <t>149812</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>188317</t>
+          <t>189434</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,98%</t>
         </is>
       </c>
     </row>
@@ -9949,12 +9949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19065</t>
+          <t>18774</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35780</t>
+          <t>36340</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9984,12 +9984,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43089</t>
+          <t>41956</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64839</t>
+          <t>64167</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>65412</t>
+          <t>66505</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>93420</t>
+          <t>93882</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6580</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18418</t>
+          <t>18577</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8188</t>
+          <t>7936</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17612</t>
+          <t>18668</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16823</t>
+          <t>16761</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32437</t>
+          <t>32794</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -10292,12 +10292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1307716</t>
+          <t>1304904</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1698103</t>
+          <t>1704609</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10307,12 +10307,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>849566</t>
+          <t>919832</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1353079</t>
+          <t>1358541</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10342,12 +10342,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2300397</t>
+          <t>2282522</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2901681</t>
+          <t>2918318</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>64,49%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>464250</t>
+          <t>469328</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>772508</t>
+          <t>775085</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>679042</t>
+          <t>674886</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1244857</t>
+          <t>1191042</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1304731</t>
+          <t>1289128</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1965170</t>
+          <t>1935616</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>42,77%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>84233</t>
+          <t>80148</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>145630</t>
+          <t>145108</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>93212</t>
+          <t>91635</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>152598</t>
+          <t>153837</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>192566</t>
+          <t>194593</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>280541</t>
+          <t>283661</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35028</t>
+          <t>37267</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69179</t>
+          <t>68994</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39837</t>
+          <t>41234</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71298</t>
+          <t>70799</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>85455</t>
+          <t>84904</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>130390</t>
+          <t>131369</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6751</t>
+          <t>6705</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20866</t>
+          <t>21966</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7328</t>
+          <t>7294</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19694</t>
+          <t>19183</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16973</t>
+          <t>16317</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>35763</t>
+          <t>35491</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>397024</t>
+          <t>400173</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>452449</t>
+          <t>451798</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>436886</t>
+          <t>438462</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>479999</t>
+          <t>478099</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>850691</t>
+          <t>850407</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>915557</t>
+          <t>920151</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,45%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>152396</t>
+          <t>152088</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>205598</t>
+          <t>202748</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>145688</t>
+          <t>144513</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>182078</t>
+          <t>181248</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>309224</t>
+          <t>307379</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>375052</t>
+          <t>375536</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,75%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21313</t>
+          <t>20003</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>43522</t>
+          <t>45128</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17793</t>
+          <t>18198</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>39149</t>
+          <t>37654</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>43505</t>
+          <t>43626</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>72883</t>
+          <t>73421</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3440</t>
+          <t>3690</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13659</t>
+          <t>12967</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4858</t>
+          <t>4842</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14109</t>
+          <t>13647</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10394</t>
+          <t>10342</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22946</t>
+          <t>23559</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -11426,12 +11426,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12778</t>
+          <t>13332</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11446,7 +11446,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7485</t>
+          <t>6522</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>4255</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15738</t>
+          <t>15593</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1997657</t>
+          <t>1996839</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2405073</t>
+          <t>2427343</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1642005</t>
+          <t>1619153</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2169002</t>
+          <t>2172446</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3772978</t>
+          <t>3790575</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4413744</t>
+          <t>4396313</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>61,96%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>769323</t>
+          <t>755368</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1092980</t>
+          <t>1090767</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1070744</t>
+          <t>1069334</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1717873</t>
+          <t>1767768</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2005318</t>
+          <t>2022136</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2734662</t>
+          <t>2727637</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,44%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>167877</t>
+          <t>168908</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>250465</t>
+          <t>249972</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,82 +11897,82 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
+          <t>7,25%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>413</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>248904</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>201568</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>282371</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>6,82%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>5,53%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>7,74%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>681</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>465962</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>399867</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>515224</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>6,57%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>5,64%</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
           <t>7,26%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>413</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>248904</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>205228</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>283073</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>6,82%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>5,63%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>7,76%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>681</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>465962</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>398187</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>513764</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>6,57%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>5,61%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>65286</t>
+          <t>66032</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>105644</t>
+          <t>106062</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>92885</t>
+          <t>94038</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>136786</t>
+          <t>135997</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>171429</t>
+          <t>173812</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>231500</t>
+          <t>229665</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -12108,12 +12108,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>20299</t>
+          <t>18971</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>42388</t>
+          <t>41492</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>19012</t>
+          <t>19744</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>36119</t>
+          <t>36663</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12158,12 +12158,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>43965</t>
+          <t>45325</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>71329</t>
+          <t>72083</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P5704-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P5704-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>491284</t>
+          <t>496319</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>556639</t>
+          <t>558048</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>604652</t>
+          <t>602961</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>672153</t>
+          <t>678202</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1122469</t>
+          <t>1122752</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1213753</t>
+          <t>1215573</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>51,8%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>249466</t>
+          <t>250092</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>306920</t>
+          <t>305440</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>333998</t>
+          <t>333220</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>400778</t>
+          <t>398854</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>601071</t>
+          <t>597547</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>683149</t>
+          <t>688537</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,34%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>148925</t>
+          <t>145669</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>197635</t>
+          <t>194836</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>187125</t>
+          <t>188078</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>238602</t>
+          <t>240049</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>349368</t>
+          <t>349895</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>418598</t>
+          <t>418626</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35614</t>
+          <t>35215</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61931</t>
+          <t>61652</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69617</t>
+          <t>67801</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>104536</t>
+          <t>105088</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>110061</t>
+          <t>111804</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>155668</t>
+          <t>157504</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3734</t>
+          <t>3817</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17176</t>
+          <t>17437</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6137</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>20879</t>
+          <t>20832</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12455</t>
+          <t>13019</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31414</t>
+          <t>32237</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>992195</t>
+          <t>986193</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1076079</t>
+          <t>1066921</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>925278</t>
+          <t>924671</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1006693</t>
+          <t>998911</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1937360</t>
+          <t>1933383</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2052361</t>
+          <t>2045527</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>62,39%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>423932</t>
+          <t>429890</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>498176</t>
+          <t>502474</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>379518</t>
+          <t>381374</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>447865</t>
+          <t>450234</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>822946</t>
+          <t>831462</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>932358</t>
+          <t>933708</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,48%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>146863</t>
+          <t>145253</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>196493</t>
+          <t>193059</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>135796</t>
+          <t>135471</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>187377</t>
+          <t>186190</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>297159</t>
+          <t>296485</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>364705</t>
+          <t>364097</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,11%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19986</t>
+          <t>18987</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41245</t>
+          <t>41923</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29574</t>
+          <t>29894</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55971</t>
+          <t>57722</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55574</t>
+          <t>57187</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>91210</t>
+          <t>92386</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5325</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,34 +1887,34 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>4995</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1223</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>12558</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
           <t>0,31%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>4995</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1230</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>11912</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,08%</t>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14150</t>
+          <t>14322</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>312377</t>
+          <t>311608</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>359069</t>
+          <t>360204</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>290510</t>
+          <t>290016</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>332946</t>
+          <t>330533</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>615926</t>
+          <t>616597</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>677966</t>
+          <t>680995</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>66,26%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>142874</t>
+          <t>141422</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>186532</t>
+          <t>186463</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>98309</t>
+          <t>98599</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>137011</t>
+          <t>136160</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>250508</t>
+          <t>250186</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>310777</t>
+          <t>307626</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>29,93%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31481</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>60330</t>
+          <t>59920</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25803</t>
+          <t>25765</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>47683</t>
+          <t>50334</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>62097</t>
+          <t>62249</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>98233</t>
+          <t>97527</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,49%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3474</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15998</t>
+          <t>16411</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5933</t>
+          <t>6098</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21205</t>
+          <t>21246</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10960</t>
+          <t>12377</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>32087</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7088</t>
+          <t>6681</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5901</t>
+          <t>6489</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1834644</t>
+          <t>1834102</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1948459</t>
+          <t>1944261</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1853243</t>
+          <t>1856356</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1969929</t>
+          <t>1976301</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3733187</t>
+          <t>3720363</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3894128</t>
+          <t>3886313</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>58,41%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>855007</t>
+          <t>853976</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>958067</t>
+          <t>955436</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>850811</t>
+          <t>850041</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>952998</t>
+          <t>951404</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1734535</t>
+          <t>1728671</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1870622</t>
+          <t>1878094</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,23%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>348583</t>
+          <t>350565</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>422460</t>
+          <t>420888</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>369511</t>
+          <t>370556</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>444594</t>
+          <t>447564</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>736502</t>
+          <t>739457</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>843129</t>
+          <t>846262</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>67226</t>
+          <t>67105</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>104532</t>
+          <t>104930</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>115279</t>
+          <t>118148</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>165480</t>
+          <t>165552</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>193783</t>
+          <t>196574</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>251358</t>
+          <t>257301</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18691</t>
+          <t>19162</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10799</t>
+          <t>10515</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>28798</t>
+          <t>28374</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>17476</t>
+          <t>18582</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>40974</t>
+          <t>40180</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>504093</t>
+          <t>507184</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>568286</t>
+          <t>570204</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>674232</t>
+          <t>673203</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>750078</t>
+          <t>744316</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1200022</t>
+          <t>1204198</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1299566</t>
+          <t>1301330</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>56,57%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>256587</t>
+          <t>253904</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>315619</t>
+          <t>311604</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>399458</t>
+          <t>400709</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>470191</t>
+          <t>465380</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>667044</t>
+          <t>667658</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>759857</t>
+          <t>760158</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,04%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>94191</t>
+          <t>95030</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>136049</t>
+          <t>137078</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>123416</t>
+          <t>123802</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>170500</t>
+          <t>171099</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>232111</t>
+          <t>230672</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>293748</t>
+          <t>294515</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14595</t>
+          <t>14971</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33853</t>
+          <t>35508</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22892</t>
+          <t>22708</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44580</t>
+          <t>44819</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41519</t>
+          <t>41508</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72585</t>
+          <t>73075</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3317</t>
+          <t>3275</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17287</t>
+          <t>17011</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>5808</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18373</t>
+          <t>19147</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10385</t>
+          <t>11209</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29432</t>
+          <t>29491</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1202753</t>
+          <t>1203165</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1293668</t>
+          <t>1294335</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>61,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>967362</t>
+          <t>971380</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1052286</t>
+          <t>1057221</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>55,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2205103</t>
+          <t>2195532</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2327491</t>
+          <t>2323258</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,59%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>477007</t>
+          <t>477969</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>560702</t>
+          <t>557433</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>499532</t>
+          <t>497222</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>581231</t>
+          <t>578256</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>995692</t>
+          <t>999862</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1112576</t>
+          <t>1110742</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,93%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>141703</t>
+          <t>144799</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>194418</t>
+          <t>194707</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>127535</t>
+          <t>128214</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>177685</t>
+          <t>174512</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>285507</t>
+          <t>284995</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>355896</t>
+          <t>353739</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13103</t>
+          <t>13883</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32149</t>
+          <t>33889</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26743</t>
+          <t>26680</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53693</t>
+          <t>52833</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46123</t>
+          <t>45290</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>79528</t>
+          <t>78396</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2872</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12904</t>
+          <t>12731</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6080</t>
+          <t>6013</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21687</t>
+          <t>21612</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10851</t>
+          <t>10799</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28993</t>
+          <t>28996</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>282112</t>
+          <t>283953</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>328396</t>
+          <t>327247</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>296362</t>
+          <t>298694</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>338917</t>
+          <t>340618</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>594710</t>
+          <t>590400</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>656987</t>
+          <t>654417</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>69,87%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>115596</t>
+          <t>117669</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>159831</t>
+          <t>161099</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>89521</t>
+          <t>88703</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>126651</t>
+          <t>125591</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>215034</t>
+          <t>216656</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>272822</t>
+          <t>273489</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,2%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20955</t>
+          <t>21027</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>45538</t>
+          <t>44617</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20281</t>
+          <t>18178</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45069</t>
+          <t>42302</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>44546</t>
+          <t>45145</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>78950</t>
+          <t>78191</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10619</t>
+          <t>10167</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7093</t>
+          <t>5900</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2246</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13261</t>
+          <t>13505</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2028286</t>
+          <t>2029811</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2146248</t>
+          <t>2145039</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1984707</t>
+          <t>1979424</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2107428</t>
+          <t>2106158</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4053792</t>
+          <t>4053493</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4219860</t>
+          <t>4218851</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>60,71%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>883944</t>
+          <t>882584</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>993655</t>
+          <t>991870</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1021258</t>
+          <t>1024356</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1135374</t>
+          <t>1136148</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1932417</t>
+          <t>1933652</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2095363</t>
+          <t>2090394</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,08%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>280623</t>
+          <t>281571</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>352999</t>
+          <t>351580</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>289982</t>
+          <t>288026</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>363475</t>
+          <t>361487</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>589904</t>
+          <t>586336</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>690214</t>
+          <t>689465</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>37664</t>
+          <t>36727</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>65504</t>
+          <t>64651</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>54672</t>
+          <t>56174</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>91653</t>
+          <t>89373</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>100364</t>
+          <t>99429</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>144167</t>
+          <t>144889</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7878</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25057</t>
+          <t>23941</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6210,77 +6210,77 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>22560</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>14427</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>34380</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>36872</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>26201</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>51572</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
           <t>0,74%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>22560</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>13467</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>35594</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>36872</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>26567</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>52393</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>349597</t>
+          <t>352635</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>406128</t>
+          <t>405521</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>440026</t>
+          <t>438034</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>505505</t>
+          <t>506231</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>807784</t>
+          <t>808132</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>895609</t>
+          <t>892743</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>51,16%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>203839</t>
+          <t>204944</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>254143</t>
+          <t>253589</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>264870</t>
+          <t>263835</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>323774</t>
+          <t>326272</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>484474</t>
+          <t>489232</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>562107</t>
+          <t>567173</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,5%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>95590</t>
+          <t>93425</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>134868</t>
+          <t>133391</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>157840</t>
+          <t>156822</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>206883</t>
+          <t>207984</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>261899</t>
+          <t>264632</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>324432</t>
+          <t>325797</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18767</t>
+          <t>18724</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38300</t>
+          <t>39250</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26492</t>
+          <t>25333</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52562</t>
+          <t>51934</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50850</t>
+          <t>50270</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83387</t>
+          <t>85578</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -7108,7 +7108,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10584</t>
+          <t>10549</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4402</t>
+          <t>4637</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18733</t>
+          <t>19925</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6219</t>
+          <t>7095</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23654</t>
+          <t>22654</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1054261</t>
+          <t>1060552</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1146118</t>
+          <t>1152873</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1002703</t>
+          <t>998005</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1093864</t>
+          <t>1087868</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2092981</t>
+          <t>2089187</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2213335</t>
+          <t>2215215</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,67%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>606842</t>
+          <t>601156</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>690094</t>
+          <t>691850</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>593934</t>
+          <t>599585</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>681927</t>
+          <t>683327</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1214813</t>
+          <t>1222981</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1336698</t>
+          <t>1345357</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>33,2%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>254265</t>
+          <t>251914</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>318552</t>
+          <t>313469</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>223257</t>
+          <t>224924</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>284901</t>
+          <t>283830</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>496692</t>
+          <t>496100</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>580084</t>
+          <t>582691</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22076</t>
+          <t>22442</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43541</t>
+          <t>45923</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21771</t>
+          <t>21315</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44071</t>
+          <t>43241</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49824</t>
+          <t>48547</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>78962</t>
+          <t>80953</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>2270</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13911</t>
+          <t>13559</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4124</t>
+          <t>3368</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16309</t>
+          <t>15776</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,47 +7835,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>14903</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>8431</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>24277</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>0,21%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>14903</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>8606</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>25229</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>312756</t>
+          <t>312656</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>361260</t>
+          <t>361853</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>315215</t>
+          <t>314911</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>363499</t>
+          <t>363061</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>641495</t>
+          <t>642757</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>711907</t>
+          <t>709128</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>64,86%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>144367</t>
+          <t>143092</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>190383</t>
+          <t>189970</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>143701</t>
+          <t>144158</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>187605</t>
+          <t>190058</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>301672</t>
+          <t>303362</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>365857</t>
+          <t>366203</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,5%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26421</t>
+          <t>26240</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>53144</t>
+          <t>53715</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,47 +8256,47 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>9,85%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>37216</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>26595</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>49859</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>6,79%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
           <t>4,85%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>9,75%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>37216</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>26833</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>52034</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>6,79%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>4,89%</t>
-        </is>
-      </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>58007</t>
+          <t>60320</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>93133</t>
+          <t>95619</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9843</t>
+          <t>10189</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,47 +8369,47 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>4286</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1027</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>10481</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>4286</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>10390</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3306</t>
+          <t>3574</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15848</t>
+          <t>15646</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -8507,7 +8507,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>5081</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5449</t>
+          <t>5532</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1762878</t>
+          <t>1759544</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1876225</t>
+          <t>1875523</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1796748</t>
+          <t>1797938</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1919166</t>
+          <t>1919092</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3584300</t>
+          <t>3595763</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3748685</t>
+          <t>3772877</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>54,75%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>985811</t>
+          <t>994051</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1097673</t>
+          <t>1099185</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1039932</t>
+          <t>1043460</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1152250</t>
+          <t>1162136</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2076192</t>
+          <t>2066663</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2224987</t>
+          <t>2220777</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>397635</t>
+          <t>396254</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>475527</t>
+          <t>475834</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>435511</t>
+          <t>433459</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>515744</t>
+          <t>519045</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>846139</t>
+          <t>847750</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>958785</t>
+          <t>962657</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>48829</t>
+          <t>49370</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>80542</t>
+          <t>80754</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>56427</t>
+          <t>56252</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>92177</t>
+          <t>92693</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9091,7 +9091,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>112651</t>
+          <t>117319</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>162415</t>
+          <t>160661</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4620</t>
+          <t>4474</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18457</t>
+          <t>17395</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,47 +9164,47 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>19348</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>11608</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>30405</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
           <t>0,55%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>19348</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>11337</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>30097</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>19642</t>
+          <t>19325</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>43037</t>
+          <t>41470</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -9605,32 +9605,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>265565</t>
+          <t>293051</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>242513</t>
+          <t>269461</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>285053</t>
+          <t>315211</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9640,32 +9640,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>355766</t>
+          <t>378406</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>333480</t>
+          <t>356076</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>377563</t>
+          <t>400435</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9675,32 +9675,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>621331</t>
+          <t>671457</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>592443</t>
+          <t>637696</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>649890</t>
+          <t>700935</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>50,28%</t>
         </is>
       </c>
     </row>
@@ -9718,32 +9718,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>141369</t>
+          <t>157768</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>124088</t>
+          <t>137534</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>161570</t>
+          <t>177728</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9753,32 +9753,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>231559</t>
+          <t>253686</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>212218</t>
+          <t>233389</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>254174</t>
+          <t>272481</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9788,32 +9788,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>372928</t>
+          <t>411454</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>348585</t>
+          <t>383995</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>401803</t>
+          <t>439954</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,56%</t>
         </is>
       </c>
     </row>
@@ -9831,32 +9831,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>68828</t>
+          <t>78865</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>56006</t>
+          <t>64984</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>83601</t>
+          <t>96106</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9866,32 +9866,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>99086</t>
+          <t>110693</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>86524</t>
+          <t>95768</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>113085</t>
+          <t>124647</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9901,32 +9901,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>167914</t>
+          <t>189558</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>149812</t>
+          <t>168780</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>189434</t>
+          <t>211576</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,18%</t>
         </is>
       </c>
     </row>
@@ -9944,32 +9944,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26454</t>
+          <t>35159</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18774</t>
+          <t>24489</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36340</t>
+          <t>51458</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9979,32 +9979,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>52251</t>
+          <t>59516</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41956</t>
+          <t>48647</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64167</t>
+          <t>74073</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10014,32 +10014,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>78704</t>
+          <t>94675</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>66505</t>
+          <t>78072</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>93882</t>
+          <t>114331</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -10057,32 +10057,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11357</t>
+          <t>12339</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6072</t>
+          <t>7563</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18577</t>
+          <t>19912</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10092,32 +10092,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>12126</t>
+          <t>14577</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7936</t>
+          <t>9235</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18668</t>
+          <t>20774</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10127,32 +10127,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>23483</t>
+          <t>26916</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16761</t>
+          <t>19843</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32794</t>
+          <t>36530</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -10170,17 +10170,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>513572</t>
+          <t>577182</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>513572</t>
+          <t>577182</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>513572</t>
+          <t>577182</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10205,17 +10205,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>750788</t>
+          <t>816878</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>750788</t>
+          <t>816878</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>750788</t>
+          <t>816878</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10240,17 +10240,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1264360</t>
+          <t>1394061</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1264360</t>
+          <t>1394061</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1264360</t>
+          <t>1394061</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10287,32 +10287,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1429768</t>
+          <t>1249732</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1304904</t>
+          <t>1195863</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1704609</t>
+          <t>1303196</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10322,32 +10322,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1207828</t>
+          <t>1230086</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>919832</t>
+          <t>1185976</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1358541</t>
+          <t>1271416</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10357,32 +10357,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2637597</t>
+          <t>2479817</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2282522</t>
+          <t>2414441</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2918318</t>
+          <t>2550716</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>58,0%</t>
         </is>
       </c>
     </row>
@@ -10400,32 +10400,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>675797</t>
+          <t>760140</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>469328</t>
+          <t>709484</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>775085</t>
+          <t>807539</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10435,32 +10435,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>837652</t>
+          <t>716166</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>674886</t>
+          <t>680363</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1191042</t>
+          <t>759454</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10470,32 +10470,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1513449</t>
+          <t>1476306</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1289128</t>
+          <t>1410335</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1935616</t>
+          <t>1541033</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>35,04%</t>
         </is>
       </c>
     </row>
@@ -10513,67 +10513,67 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>117970</t>
+          <t>137722</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>80148</t>
+          <t>114936</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>145108</t>
+          <t>163552</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
+          <t>7,34%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>137569</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>117170</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>159388</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
           <t>6,34%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>123514</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>91635</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>153837</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>5,52%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10583,32 +10583,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>241484</t>
+          <t>275291</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>194593</t>
+          <t>245069</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>283661</t>
+          <t>309131</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -10626,32 +10626,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>52830</t>
+          <t>65773</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37267</t>
+          <t>51335</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68994</t>
+          <t>83442</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10661,32 +10661,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>55327</t>
+          <t>67690</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41234</t>
+          <t>54531</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70799</t>
+          <t>81402</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10696,32 +10696,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>108157</t>
+          <t>133463</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84904</t>
+          <t>113781</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>131369</t>
+          <t>153959</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -10739,32 +10739,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>12518</t>
+          <t>14252</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6705</t>
+          <t>8381</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21966</t>
+          <t>22751</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10774,32 +10774,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>12293</t>
+          <t>18644</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7294</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19183</t>
+          <t>28844</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10809,32 +10809,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>24810</t>
+          <t>32896</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16317</t>
+          <t>23362</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>35491</t>
+          <t>46653</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -10852,17 +10852,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2288883</t>
+          <t>2227619</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2288883</t>
+          <t>2227619</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2288883</t>
+          <t>2227619</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10887,17 +10887,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2236614</t>
+          <t>2170155</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2236614</t>
+          <t>2170155</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2236614</t>
+          <t>2170155</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10922,17 +10922,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4525497</t>
+          <t>4397774</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4525497</t>
+          <t>4397774</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4525497</t>
+          <t>4397774</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10969,32 +10969,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>426944</t>
+          <t>472253</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>400173</t>
+          <t>443200</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>451798</t>
+          <t>499133</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11004,32 +11004,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>459540</t>
+          <t>506265</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>438462</t>
+          <t>484359</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>478099</t>
+          <t>527733</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11039,32 +11039,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>886485</t>
+          <t>978518</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>850407</t>
+          <t>942552</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>920151</t>
+          <t>1012613</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>67,74%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,1%</t>
         </is>
       </c>
     </row>
@@ -11082,32 +11082,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>175501</t>
+          <t>185360</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>152088</t>
+          <t>162122</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>202748</t>
+          <t>212140</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11117,32 +11117,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>162867</t>
+          <t>184264</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>144513</t>
+          <t>164919</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>181248</t>
+          <t>206869</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11152,32 +11152,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>338368</t>
+          <t>369625</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>307379</t>
+          <t>339097</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>375536</t>
+          <t>405901</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,1%</t>
         </is>
       </c>
     </row>
@@ -11195,32 +11195,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>30261</t>
+          <t>35355</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20003</t>
+          <t>24283</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>45128</t>
+          <t>48705</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11230,17 +11230,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>26303</t>
+          <t>29197</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>18198</t>
+          <t>20631</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>37654</t>
+          <t>40838</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11265,32 +11265,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>56565</t>
+          <t>64551</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>43626</t>
+          <t>50018</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>73421</t>
+          <t>82862</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -11308,32 +11308,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7452</t>
+          <t>10368</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3690</t>
+          <t>5535</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12967</t>
+          <t>17399</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11343,32 +11343,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8622</t>
+          <t>10998</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4842</t>
+          <t>6702</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13647</t>
+          <t>18049</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11378,32 +11378,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>16074</t>
+          <t>21366</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10342</t>
+          <t>14565</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23559</t>
+          <t>30669</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -11421,32 +11421,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>5554</t>
+          <t>7290</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1931</t>
+          <t>2698</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13332</t>
+          <t>15871</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11456,22 +11456,22 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6522</t>
+          <t>7235</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -11491,32 +11491,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>8525</t>
+          <t>10469</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4255</t>
+          <t>4926</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15593</t>
+          <t>18739</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -11534,17 +11534,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>645713</t>
+          <t>710626</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>645713</t>
+          <t>710626</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>645713</t>
+          <t>710626</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11569,17 +11569,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>660304</t>
+          <t>733902</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>660304</t>
+          <t>733902</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>660304</t>
+          <t>733902</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11604,17 +11604,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1306017</t>
+          <t>1444528</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1306017</t>
+          <t>1444528</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1306017</t>
+          <t>1444528</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11651,32 +11651,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2122278</t>
+          <t>2015035</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1996839</t>
+          <t>1951517</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2427343</t>
+          <t>2078731</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11686,32 +11686,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2023135</t>
+          <t>2114757</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1619153</t>
+          <t>2062033</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2172446</t>
+          <t>2171769</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>55,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11721,32 +11721,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>4145413</t>
+          <t>4129792</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3790575</t>
+          <t>4049125</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4396313</t>
+          <t>4219333</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>58,31%</t>
         </is>
       </c>
     </row>
@@ -11764,32 +11764,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>992668</t>
+          <t>1103268</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>755368</t>
+          <t>1043742</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1090767</t>
+          <t>1162148</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11799,32 +11799,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1232077</t>
+          <t>1154117</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1069334</t>
+          <t>1105791</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1767768</t>
+          <t>1202850</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11834,32 +11834,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2224745</t>
+          <t>2257385</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2022136</t>
+          <t>2185846</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2727637</t>
+          <t>2335613</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>32,28%</t>
         </is>
       </c>
     </row>
@@ -11877,32 +11877,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>217059</t>
+          <t>251941</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>168908</t>
+          <t>222957</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>249972</t>
+          <t>285170</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11912,32 +11912,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>248904</t>
+          <t>277459</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>201568</t>
+          <t>253231</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>282371</t>
+          <t>309344</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11947,32 +11947,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>465962</t>
+          <t>529400</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>399867</t>
+          <t>487820</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>515224</t>
+          <t>575478</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,95%</t>
         </is>
       </c>
     </row>
@@ -11990,32 +11990,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>86736</t>
+          <t>111300</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>66032</t>
+          <t>92380</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>106062</t>
+          <t>137569</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12025,32 +12025,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>116200</t>
+          <t>138203</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>94038</t>
+          <t>118274</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>135997</t>
+          <t>158844</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12060,32 +12060,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>202935</t>
+          <t>249503</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>173812</t>
+          <t>220161</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>229665</t>
+          <t>277870</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -12103,32 +12103,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>29428</t>
+          <t>33882</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>18971</t>
+          <t>23608</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>41492</t>
+          <t>46625</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12138,32 +12138,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>27390</t>
+          <t>36399</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>19744</t>
+          <t>26966</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>36663</t>
+          <t>47602</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12173,32 +12173,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>56818</t>
+          <t>70282</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>45325</t>
+          <t>55967</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>72083</t>
+          <t>87207</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -12216,17 +12216,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3448168</t>
+          <t>3515427</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3448168</t>
+          <t>3515427</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3448168</t>
+          <t>3515427</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12251,17 +12251,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3647706</t>
+          <t>3720936</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3647706</t>
+          <t>3720936</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3647706</t>
+          <t>3720936</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12286,17 +12286,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7095874</t>
+          <t>7236363</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7095874</t>
+          <t>7236363</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7095874</t>
+          <t>7236363</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
